--- a/BGNE.xlsx
+++ b/BGNE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC36D148-A9BF-4DC4-A5F7-107314447199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEDC24C-96DD-4DD8-8B4E-0D48A48F058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27015" yWindow="750" windowWidth="26490" windowHeight="19650" xr2:uid="{ECF363C9-B515-44DE-94FD-36ED756098F0}"/>
+    <workbookView xWindow="20880" yWindow="3490" windowWidth="19050" windowHeight="16100" xr2:uid="{ECF363C9-B515-44DE-94FD-36ED756098F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
     <t>LAG-3</t>
   </si>
   <si>
-    <t>Q224</t>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -692,15 +692,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2391AD9C-ECF7-494A-A17A-9227C0123BFA}">
   <dimension ref="B2:M19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
@@ -726,10 +726,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
@@ -750,14 +750,14 @@
         <v>1</v>
       </c>
       <c r="L3" s="11">
-        <f>1361.082567/13</f>
-        <v>104.69865899999999</v>
+        <f>1445.262342/13</f>
+        <v>111.1740263076923</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
       <c r="C4" t="s">
         <v>19</v>
@@ -780,11 +780,11 @@
       </c>
       <c r="L4" s="11">
         <f>L2*L3</f>
-        <v>19892.745209999997</v>
+        <v>35130.992313230767</v>
       </c>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>36</v>
       </c>
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="L5" s="11">
-        <v>2617.931</v>
+        <v>4791.6760000000004</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
@@ -817,13 +817,14 @@
         <v>4</v>
       </c>
       <c r="L6" s="11">
-        <v>1036.9280000000001</v>
+        <f>116.14+962.515</f>
+        <v>1078.655</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>61</v>
       </c>
@@ -833,10 +834,10 @@
       </c>
       <c r="L7" s="11">
         <f>L4-L5+L6</f>
-        <v>18311.742209999997</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+        <v>31417.971313230766</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>38</v>
       </c>
@@ -849,7 +850,7 @@
       </c>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -863,7 +864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
       <c r="C10" t="s">
         <v>41</v>
@@ -879,7 +880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>48</v>
       </c>
@@ -888,7 +889,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>62</v>
@@ -898,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>50</v>
       </c>
@@ -907,7 +908,7 @@
       </c>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>65</v>
       </c>
@@ -916,7 +917,7 @@
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>63</v>
       </c>
@@ -925,7 +926,7 @@
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>52</v>
       </c>
@@ -934,7 +935,7 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>56</v>
       </c>
@@ -943,7 +944,7 @@
       </c>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="C18" t="s">
         <v>59</v>
@@ -953,7 +954,7 @@
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>54</v>
       </c>
@@ -974,18 +975,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9631FD-6091-4033-9588-A2B60C306ED2}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="10"/>
+    <col min="3" max="14" width="9.1796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C2" s="10" t="s">
         <v>24</v>
       </c>
@@ -1023,7 +1024,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -1034,7 +1035,7 @@
         <v>104.3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1045,7 +1046,7 @@
         <v>87.6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>23</v>
       </c>
